--- a/data/trans_orig/IP18B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP18B-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>596</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4639</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6094</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>8231</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41250</t>
+          <t>41088</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54225</t>
+          <t>54117</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50871</t>
+          <t>50485</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62176</t>
+          <t>62041</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94891</t>
+          <t>94047</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112878</t>
+          <t>111830</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>76,88%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15572</t>
+          <t>15627</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28074</t>
+          <t>28745</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10181</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21510</t>
+          <t>21466</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>29056</t>
+          <t>29737</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>46606</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17640</t>
+          <t>18100</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33405</t>
+          <t>33297</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17125</t>
+          <t>17904</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32924</t>
+          <t>33231</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39718</t>
+          <t>39150</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60718</t>
+          <t>61299</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>264557</t>
+          <t>265556</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>290538</t>
+          <t>291887</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>293716</t>
+          <t>293071</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>321189</t>
+          <t>321645</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>566413</t>
+          <t>568143</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>605006</t>
+          <t>606407</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,32%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57917</t>
+          <t>56588</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81847</t>
+          <t>81078</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65892</t>
+          <t>67753</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92101</t>
+          <t>92279</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>130639</t>
+          <t>132008</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>166898</t>
+          <t>165611</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14264</t>
+          <t>14061</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13904</t>
+          <t>13619</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11725</t>
+          <t>11864</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25242</t>
+          <t>24691</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>111092</t>
+          <t>110192</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127945</t>
+          <t>127697</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95265</t>
+          <t>95319</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111826</t>
+          <t>112504</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>212056</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>236224</t>
+          <t>234714</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>79,78%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18315</t>
+          <t>18779</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33198</t>
+          <t>33476</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20852</t>
+          <t>20378</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35745</t>
+          <t>35641</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42892</t>
+          <t>42807</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>64528</t>
+          <t>64120</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,79%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26487</t>
+          <t>27068</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44683</t>
+          <t>45931</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26045</t>
+          <t>26424</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43599</t>
+          <t>45317</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56996</t>
+          <t>57451</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83957</t>
+          <t>83304</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>429210</t>
+          <t>429125</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>464163</t>
+          <t>462620</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>451682</t>
+          <t>450483</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>485351</t>
+          <t>486016</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>890803</t>
+          <t>891050</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>941489</t>
+          <t>938193</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,65%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>100459</t>
+          <t>100758</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>132024</t>
+          <t>131838</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>106155</t>
+          <t>105511</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>139192</t>
+          <t>139623</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>215268</t>
+          <t>217502</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>261899</t>
+          <t>263541</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7750</t>
+          <t>7235</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1732</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>8191</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3629</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12408</t>
+          <t>12450</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60547</t>
+          <t>59454</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73992</t>
+          <t>72993</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49072</t>
+          <t>48989</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62133</t>
+          <t>61838</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112397</t>
+          <t>112573</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131456</t>
+          <t>131594</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,28%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11266</t>
+          <t>12277</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24188</t>
+          <t>25240</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12473</t>
+          <t>12605</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25365</t>
+          <t>25121</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27499</t>
+          <t>27510</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>45740</t>
+          <t>44977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12302</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25905</t>
+          <t>26528</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24395</t>
+          <t>23841</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42394</t>
+          <t>42427</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40731</t>
+          <t>40602</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>63903</t>
+          <t>62858</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>319145</t>
+          <t>321907</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>349023</t>
+          <t>348563</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>352669</t>
+          <t>353854</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382917</t>
+          <t>383675</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>682525</t>
+          <t>682025</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>723660</t>
+          <t>724446</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,52%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59362</t>
+          <t>60671</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86621</t>
+          <t>85679</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59847</t>
+          <t>60907</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86213</t>
+          <t>86016</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>127926</t>
+          <t>127358</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>164908</t>
+          <t>165706</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8246</t>
+          <t>7926</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19552</t>
+          <t>19742</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,49 +3715,49 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>12,59%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>14457</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>9324</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>20588</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>8,76%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>5,65%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
           <t>12,47%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>14457</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9179</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>21349</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>8,76%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>12,94%</t>
-        </is>
-      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>39</t>
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20004</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36558</t>
+          <t>36582</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>117021</t>
+          <t>116919</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133695</t>
+          <t>133435</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120219</t>
+          <t>120993</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>137767</t>
+          <t>137818</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>242906</t>
+          <t>241984</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>266563</t>
+          <t>266092</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,69%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>12250</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25623</t>
+          <t>26369</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14102</t>
+          <t>14602</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28921</t>
+          <t>28515</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30134</t>
+          <t>29580</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49983</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26031</t>
+          <t>26679</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44964</t>
+          <t>45399</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>40571</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63434</t>
+          <t>63559</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72282</t>
+          <t>72314</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>100646</t>
+          <t>99445</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>507738</t>
+          <t>510554</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>543449</t>
+          <t>545942</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>534908</t>
+          <t>535716</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>572384</t>
+          <t>572917</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1056223</t>
+          <t>1057390</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1107448</t>
+          <t>1107292</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,81%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>92957</t>
+          <t>92977</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>126240</t>
+          <t>125513</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>95380</t>
+          <t>95640</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>127122</t>
+          <t>128680</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>196981</t>
+          <t>200601</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>242092</t>
+          <t>243563</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,55%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>9268</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>547</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11584</t>
+          <t>12061</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32811</t>
+          <t>32153</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43811</t>
+          <t>43458</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41371</t>
+          <t>41573</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52664</t>
+          <t>53077</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77923</t>
+          <t>77713</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>93684</t>
+          <t>93860</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,62%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8300</t>
+          <t>8295</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>18615</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8678</t>
+          <t>8572</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19392</t>
+          <t>19765</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20013</t>
+          <t>19477</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34940</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12257</t>
+          <t>12251</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25817</t>
+          <t>26145</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18753</t>
+          <t>18635</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36288</t>
+          <t>35927</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35032</t>
+          <t>34996</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56721</t>
+          <t>56074</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>307341</t>
+          <t>305419</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>336871</t>
+          <t>336506</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>292500</t>
+          <t>292777</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>325471</t>
+          <t>324567</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>606789</t>
+          <t>606472</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>649974</t>
+          <t>652761</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,41%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84352</t>
+          <t>84653</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111630</t>
+          <t>114663</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>89873</t>
+          <t>88862</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119817</t>
+          <t>118056</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>183670</t>
+          <t>180757</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>224756</t>
+          <t>223060</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12254</t>
+          <t>12725</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>7452</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19501</t>
+          <t>19365</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>11804</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26446</t>
+          <t>26193</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>114725</t>
+          <t>115081</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131889</t>
+          <t>132044</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>127652</t>
+          <t>128688</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>145933</t>
+          <t>145320</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>249747</t>
+          <t>248906</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>274275</t>
+          <t>272489</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,16%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16638</t>
+          <t>17172</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32306</t>
+          <t>32487</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16015</t>
+          <t>16346</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31534</t>
+          <t>30435</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36104</t>
+          <t>37819</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>57541</t>
+          <t>58142</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21205</t>
+          <t>22215</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39404</t>
+          <t>39758</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30280</t>
+          <t>31493</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52061</t>
+          <t>53121</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57203</t>
+          <t>57679</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84244</t>
+          <t>84218</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>463851</t>
+          <t>463582</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>501824</t>
+          <t>499803</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>476442</t>
+          <t>475281</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>514206</t>
+          <t>514934</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>948962</t>
+          <t>952048</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1004038</t>
+          <t>1003988</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,81%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>118194</t>
+          <t>119075</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>153281</t>
+          <t>152959</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>121365</t>
+          <t>122331</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>157614</t>
+          <t>158757</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>251289</t>
+          <t>251407</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>300680</t>
+          <t>299076</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2558</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>4152</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4394</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>29,6%</t>
         </is>
       </c>
     </row>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2494</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>4575</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8561</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14598</t>
+          <t>14566</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3365</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4649</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>605</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3559</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12773</t>
+          <t>11973</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3907</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>13357</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22792</t>
+          <t>22289</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46388</t>
+          <t>46881</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58263</t>
+          <t>57555</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>58964</t>
+          <t>59030</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>75167</t>
+          <t>75466</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>110503</t>
+          <t>109777</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>130270</t>
+          <t>129162</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,01%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11334</t>
+          <t>11240</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9261</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24209</t>
+          <t>24133</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14725</t>
+          <t>14094</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31304</t>
+          <t>30803</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7559</t>
+          <t>8269</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9012</t>
+          <t>8756</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13778</t>
+          <t>14305</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17009</t>
+          <t>16584</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24199</t>
+          <t>23756</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14580</t>
+          <t>14542</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24456</t>
+          <t>24415</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34041</t>
+          <t>34712</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46113</t>
+          <t>46691</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,89%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>765</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5985</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3012</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11677</t>
+          <t>11551</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15130</t>
+          <t>14479</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17965</t>
+          <t>18001</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20784</t>
+          <t>20142</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17084</t>
+          <t>18026</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33511</t>
+          <t>33082</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>70726</t>
+          <t>71288</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>84759</t>
+          <t>84744</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>85091</t>
+          <t>84853</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>104228</t>
+          <t>104410</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>161722</t>
+          <t>162218</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>186303</t>
+          <t>185488</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>5958</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16241</t>
+          <t>16520</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15913</t>
+          <t>15061</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32454</t>
+          <t>33374</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24196</t>
+          <t>24229</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>44452</t>
+          <t>43879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP18B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP18B-Estudios-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores en función de la especialidad del doctor por el que fueron atendidos en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Menores en función de la especialidad médica por el que fueron atendidos en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -728,69 +728,69 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5858</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>1935</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5174</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5177</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,71%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>7,25%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2050</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5636</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>6</t>
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8231</t>
+          <t>7591</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>56808</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>50410</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>62189</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>76,71%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>68,07%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>83,98%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>47870</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>41088</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>54117</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>40504</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>53291</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>67,05%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>57,55%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>75,8%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>56808</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>50485</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>62041</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>76,71%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94047</t>
+          <t>95195</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>111830</t>
+          <t>112678</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>77,47%</t>
         </is>
       </c>
     </row>
@@ -949,72 +949,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15199</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10052</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21117</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>20,52%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>13,57%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>28,51%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>21591</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15627</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>28745</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>16317</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>29316</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>30,24%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>21,89%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>40,26%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>15199</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>10327</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>21466</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>20,52%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>29737</t>
+          <t>28838</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>46606</t>
+          <t>45698</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -1062,57 +1062,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>74056</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>74056</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>74056</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>71397</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>71397</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>71397</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>74056</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>74056</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>74056</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>24154</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17559</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>32749</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4,27%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>24873</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>18100</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>33297</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>17832</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>33436</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>6,67%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8,93%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>24154</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>17904</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>33231</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>5,87%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39150</t>
+          <t>39963</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61299</t>
+          <t>60097</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -1292,72 +1292,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>307685</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>293754</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>321414</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>74,81%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>71,42%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>78,15%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>422</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>279129</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>265556</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>291887</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>264116</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>291122</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>74,84%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>71,2%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>78,26%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>307685</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>293071</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>321645</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>74,81%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>568143</t>
+          <t>566036</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>606407</t>
+          <t>606383</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1405,72 +1405,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>79463</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>66879</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>93284</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>19,32%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>16,26%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22,68%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>68966</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>56588</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>81078</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>58392</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>82601</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>18,49%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,17%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>21,74%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>79463</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>67753</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>92279</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>19,32%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>132008</t>
+          <t>130403</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>165611</t>
+          <t>167693</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -1518,57 +1518,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>411303</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>411303</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>411303</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>562</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>372968</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>372968</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>372968</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>411303</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>411303</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>411303</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1635,72 +1635,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8052</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4493</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>13467</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5,75%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>9,62%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>9031</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5117</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>14061</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>5264</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>14962</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>5,85%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,11%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>8052</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>4502</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>13619</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>5,75%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>11132</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24691</t>
+          <t>24306</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -1748,72 +1748,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>104124</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>95478</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>112134</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>74,42%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>68,24%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>80,14%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>120062</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>110192</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>127697</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>111334</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>127849</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>77,81%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>71,42%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>82,76%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>104124</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>95319</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>112504</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>74,42%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>212056</t>
+          <t>212673</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>234714</t>
+          <t>235833</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>80,16%</t>
         </is>
       </c>
     </row>
@@ -1861,72 +1861,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27745</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21175</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>36651</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>19,83%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>15,13%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>26,19%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>25202</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>18779</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>33476</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>18142</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>32991</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>16,33%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12,17%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>21,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>27745</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>20378</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>35641</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>19,83%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42807</t>
+          <t>43051</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>64120</t>
+          <t>64683</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -1974,57 +1974,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>139921</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>139921</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>139921</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>154294</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>154294</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>154294</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>139921</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>139921</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>139921</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2091,72 +2091,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>34256</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>25433</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>43969</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,07%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7,03%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>35838</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>27068</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>45931</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>28627</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>47181</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,99%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>34256</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>26424</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>45317</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57451</t>
+          <t>56819</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83304</t>
+          <t>83592</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -2204,72 +2204,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>468617</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>450883</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>486297</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>74,95%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>72,11%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>77,77%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>668</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>447062</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>429125</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>462620</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>428851</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>462449</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>74,68%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>71,68%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>77,28%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>468617</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>450483</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>486016</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>74,95%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>891050</t>
+          <t>890894</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>938193</t>
+          <t>939404</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,75%</t>
         </is>
       </c>
     </row>
@@ -2317,72 +2317,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>122407</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>105548</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>139367</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>19,58%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>16,88%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>22,29%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>115759</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>100758</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>131838</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>101146</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>133389</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>19,34%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>16,83%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>22,02%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>122407</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>105511</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>139623</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>19,58%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>217502</t>
+          <t>218791</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>263541</t>
+          <t>261755</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -2430,57 +2430,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>625280</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>625280</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>625280</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>893</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>598659</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>598659</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>598659</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>625280</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>625280</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>625280</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2593,13 +2593,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores en función de la especialidad del doctor por el que fueron atendidos en 2012 (tasa de respuesta: 99,35%)</t>
+          <t>Menores en función de la especialidad médica por el que fueron atendidos en 2012 (tasa de respuesta: 99,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2610,7 +2610,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3958</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1590</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8116</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,39%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3300</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1272</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7235</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7341</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,76%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3958</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1432</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8191</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12450</t>
+          <t>13205</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>55704</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>48160</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>61605</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>71,31%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>61,65%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>78,87%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>66853</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>59454</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>72993</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>60133</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>73345</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>76,08%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>67,66%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>83,06%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>55704</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>48989</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>61838</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>71,31%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112573</t>
+          <t>112433</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131594</t>
+          <t>131968</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,5%</t>
         </is>
       </c>
     </row>
@@ -3004,72 +3004,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18452</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13347</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>25690</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>23,62%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>17,09%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>32,89%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>17724</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>12277</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>25240</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>12100</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>24381</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>20,17%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>13,97%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>28,72%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>18452</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12605</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>25121</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>23,62%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27510</t>
+          <t>27820</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>44977</t>
+          <t>46337</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,92%</t>
         </is>
       </c>
     </row>
@@ -3117,57 +3117,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>78114</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>78114</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>78114</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>87877</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>87877</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>87877</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>78114</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>78114</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>78114</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>32385</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>24651</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>41809</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6,84%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8,83%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>18208</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>12102</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>26528</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>11912</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>25694</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>4,27%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,23%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>32385</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>23841</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>42427</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>6,84%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40602</t>
+          <t>40014</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62858</t>
+          <t>62080</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -3347,72 +3347,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>369259</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>355249</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>384327</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>77,95%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>74,99%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>81,13%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>487</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>334830</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>321907</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>348563</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>322108</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>348012</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>78,61%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>75,57%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>81,83%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>369259</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>353854</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>383675</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>77,95%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>682025</t>
+          <t>682182</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>724446</t>
+          <t>723160</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,38%</t>
         </is>
       </c>
     </row>
@@ -3460,72 +3460,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>72068</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>59784</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>86417</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15,21%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12,62%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>18,24%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>72926</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>60671</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>85679</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>60102</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>85935</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>17,12%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,24%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20,11%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>72068</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>60907</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>86016</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>15,21%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>127358</t>
+          <t>129780</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>165706</t>
+          <t>164656</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -3573,57 +3573,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>473711</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>473711</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>473711</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>617</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>425964</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>425964</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>425964</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>473711</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>473711</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>473711</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3690,72 +3690,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14457</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9413</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>20859</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8,76%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>12,64%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>13070</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7926</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19742</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>8164</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>19833</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>8,34%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,06%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>12,59%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>14457</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9324</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>20588</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>8,76%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>19954</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36582</t>
+          <t>36511</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -3803,72 +3803,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>129606</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>121048</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>137637</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>78,53%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>73,35%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>83,4%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>125689</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>116919</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>133435</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>116429</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>133235</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>80,18%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>74,58%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>85,12%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>129606</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>120993</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>137818</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>78,53%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>241984</t>
+          <t>243091</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>266092</t>
+          <t>267117</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>83,01%</t>
         </is>
       </c>
     </row>
@@ -3916,72 +3916,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20972</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15001</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>29091</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>12,71%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>9,09%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>17,63%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>18008</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12250</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>26369</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>11592</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>25848</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>11,49%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,81%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>16,82%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>20972</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>14602</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>28515</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>12,71%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29580</t>
+          <t>29882</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>49580</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,41%</t>
         </is>
       </c>
     </row>
@@ -4029,57 +4029,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>165036</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>165036</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>165036</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>156768</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>156768</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>156768</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>165036</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>165036</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>165036</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4146,72 +4146,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>50800</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>40575</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>63220</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,09%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,82%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>34578</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>26679</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>45399</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>26505</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>44685</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,16%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>50800</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>40571</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>63559</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>7,09%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72314</t>
+          <t>71373</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99445</t>
+          <t>100846</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -4259,72 +4259,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>786</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>554569</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>536043</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>572691</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>77,36%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>74,78%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>79,89%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>764</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>527372</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>510554</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>545942</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>510262</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>544223</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>78,64%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>76,13%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>81,41%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>786</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>554569</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>535716</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>572917</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>77,36%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1057390</t>
+          <t>1056723</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1107292</t>
+          <t>1105600</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -4372,72 +4372,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>111492</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>96123</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>127772</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>15,55%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>13,41%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>17,82%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>108659</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>92977</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>125513</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>93261</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>124927</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>16,2%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>13,86%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>18,72%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>111492</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>95640</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>128680</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>15,55%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>200601</t>
+          <t>197570</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>243563</t>
+          <t>241428</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -4485,57 +4485,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1019</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>716861</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>716861</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>716861</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>965</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>670609</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>670609</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>670609</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1019</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>716861</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>716861</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>716861</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4648,13 +4648,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores en función de la especialidad del doctor por el que fueron atendidos en 2016 (tasa de respuesta: 99,18%)</t>
+          <t>Menores en función de la especialidad médica por el que fueron atendidos en 2016 (tasa de respuesta: 99,18%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4665,7 +4665,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4833,72 +4833,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1858</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5076</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,03%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4646</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2138</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9268</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9429</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>8,27%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,51%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1858</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5104</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12061</t>
+          <t>11865</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -4946,72 +4946,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>47944</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>42340</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>53223</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>75,82%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>66,96%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>84,17%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>38533</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>32153</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>43458</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>32365</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>43393</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>68,63%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>57,27%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>77,4%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>47944</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>41573</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>53077</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>75,82%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77713</t>
+          <t>77843</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>93860</t>
+          <t>94366</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>79,05%</t>
         </is>
       </c>
     </row>
@@ -5059,72 +5059,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13432</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8634</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19414</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>21,24%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>13,65%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>30,7%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>12968</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>8295</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>18615</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>8747</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>19478</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>23,1%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>14,77%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>33,15%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>13432</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>8572</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>19765</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>21,24%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19477</t>
+          <t>19010</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34742</t>
+          <t>35153</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -5172,57 +5172,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>63234</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>63234</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>63234</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>56147</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>56147</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>56147</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>63234</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>63234</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>63234</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5289,72 +5289,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>26318</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18859</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>35955</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5,99%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8,18%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>18420</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>12251</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>26145</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>12318</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>25098</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>4,21%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,97%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>26318</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>18635</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>35927</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>5,99%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34996</t>
+          <t>34715</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56074</t>
+          <t>55916</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -5402,72 +5402,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>309511</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>294391</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>326757</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>70,45%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>67,01%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>74,37%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>496</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>320936</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>305419</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>336506</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>305261</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>335556</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>73,29%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>69,74%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>76,84%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>309511</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>292777</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>324567</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>70,45%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>606472</t>
+          <t>608821</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>652761</t>
+          <t>652655</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,4%</t>
         </is>
       </c>
     </row>
@@ -5515,72 +5515,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>103515</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>87602</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>118673</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>23,56%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>19,94%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>27,01%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>98560</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>84653</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>114663</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>84912</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>113850</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>22,51%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,33%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>26,18%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>103515</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>88862</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>118056</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>23,56%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>180757</t>
+          <t>180737</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>223060</t>
+          <t>221661</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -5628,57 +5628,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>439344</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>439344</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>439344</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>663</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>437916</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>437916</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>437916</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>439344</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>439344</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>439344</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5745,72 +5745,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12483</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7338</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18741</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,21%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10,83%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>6603</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3297</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>12725</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>3207</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>12222</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>4,27%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,23%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>12483</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>7452</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>19365</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>7,21%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11804</t>
+          <t>12871</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26193</t>
+          <t>27698</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -5858,72 +5858,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>137504</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>128801</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>145662</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>79,47%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>74,44%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>84,18%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>123920</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>115081</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>132044</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>115214</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>131744</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>80,14%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>74,42%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>85,4%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>137504</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>128688</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>145320</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>79,47%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>248906</t>
+          <t>249413</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>272489</t>
+          <t>272907</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,29%</t>
         </is>
       </c>
     </row>
@@ -5971,72 +5971,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23042</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16792</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>31280</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>13,32%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>9,7%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>18,08%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>24105</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>17172</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>32487</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>17027</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>32455</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>15,59%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>11,11%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>21,01%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>23042</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>16346</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>30435</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>13,32%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37819</t>
+          <t>37537</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>58142</t>
+          <t>58666</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -6084,57 +6084,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173030</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173030</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173030</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>154627</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>154627</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>154627</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173030</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173030</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173030</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6201,72 +6201,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>40659</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>30786</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>51618</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>29668</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>22215</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>39758</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>21673</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>39506</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>4,57%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,13%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>40659</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>31493</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>53121</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57679</t>
+          <t>55962</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84218</t>
+          <t>83383</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -6314,72 +6314,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>494960</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>474392</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>513633</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>73,26%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>70,22%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>76,03%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>741</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>483388</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>463582</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>499803</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>464037</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>499343</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>74,52%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>71,46%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>77,05%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>494960</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>475281</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>514934</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>73,26%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>952048</t>
+          <t>950550</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1003988</t>
+          <t>1004574</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,86%</t>
         </is>
       </c>
     </row>
@@ -6427,72 +6427,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>139989</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>122748</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>160437</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>20,72%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>18,17%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>23,75%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>135633</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>119075</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>152959</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>120017</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>153096</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>20,91%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>18,36%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>23,58%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>139989</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>122331</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>158757</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>20,72%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>251407</t>
+          <t>250309</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>299076</t>
+          <t>300018</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -6540,57 +6540,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>965</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>675608</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>675608</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>675608</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>977</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>648689</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>648689</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>648689</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>965</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>675608</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>675608</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>675608</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6703,13 +6703,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores en función de la especialidad del doctor por el que fueron atendidos en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores en función de la especialidad médica por el que fueron atendidos en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6720,7 +6720,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>938</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>596</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4152</t>
+          <t>2489</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1534</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -6973,12 +6973,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4729</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>34,49%</t>
         </is>
       </c>
     </row>
@@ -7001,72 +7001,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7138</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>78,52%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>45,14%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4746</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2665</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6048</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>72,51%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>40,71%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>92,41%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7471</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>12217</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>7697</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14566</t>
+          <t>13493</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>89,68%</t>
         </is>
       </c>
     </row>
@@ -7114,72 +7114,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4386</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11,17%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>48,24%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1274</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1291</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3365</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>19,46%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3207</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>21,69%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>51,41%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>4005</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>11,22%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2332</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>644</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>42,6%</t>
         </is>
       </c>
     </row>
@@ -7227,57 +7227,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7344,72 +7344,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7225</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3668</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12516</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8,62%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4,38%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>14,93%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7191</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3559</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11973</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,86%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,37%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18,08%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7694</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>3870</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13357</t>
+          <t>14193</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>14884</t>
+          <t>14758</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9822</t>
+          <t>9390</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22289</t>
+          <t>22498</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -7457,72 +7457,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>61827</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>53323</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>68809</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>73,77%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>63,63%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>82,1%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>52800</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>46881</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>57555</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>79,71%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>70,78%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>86,89%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>68523</t>
+          <t>49319</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>59030</t>
+          <t>42796</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>75466</t>
+          <t>54810</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>121323</t>
+          <t>111146</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>109777</t>
+          <t>100757</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>129162</t>
+          <t>119961</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,59%</t>
         </is>
       </c>
     </row>
@@ -7570,72 +7570,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14755</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8862</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>24971</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>17,61%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10,57%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>29,8%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6247</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3314</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11240</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,43%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,97%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15032</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8788</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24133</t>
+          <t>11470</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21279</t>
+          <t>21129</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14094</t>
+          <t>13722</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30803</t>
+          <t>31255</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -7683,57 +7683,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>83807</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>83807</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>83807</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>66238</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>66238</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>66238</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>91249</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91249</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>91249</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>157487</t>
+          <t>147033</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>157487</t>
+          <t>147033</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>157487</t>
+          <t>147033</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7800,72 +7800,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4395</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1619</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8884</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>15,25%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5,62%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>30,82%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4009</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8269</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>14,56%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,54%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>30,04%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8560</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14305</t>
+          <t>13755</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,94%</t>
         </is>
       </c>
     </row>
@@ -7913,72 +7913,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18147</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13072</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22081</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>62,96%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>45,35%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>76,61%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>20930</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>16584</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>23756</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>76,02%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>60,24%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>86,29%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19910</t>
+          <t>19641</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14542</t>
+          <t>15111</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24415</t>
+          <t>22492</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>40841</t>
+          <t>37787</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34712</t>
+          <t>31419</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46691</t>
+          <t>42486</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>77,03%</t>
         </is>
       </c>
     </row>
@@ -8026,72 +8026,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6283</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3014</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>11204</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>21,8%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>10,46%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>38,87%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2591</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>765</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5971</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>9,41%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>21,69%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6667</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>793</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>6059</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>9259</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14479</t>
+          <t>14434</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -8139,57 +8139,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>28824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>28824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>28824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>27531</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>27531</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>27531</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>55155</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>55155</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>55155</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8256,72 +8256,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12557</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7436</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>19855</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10,32%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,11%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>16,31%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>11726</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7330</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>18001</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>11,69%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,31%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>17,94%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12929</t>
+          <t>12295</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20142</t>
+          <t>19462</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>24655</t>
+          <t>24851</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18026</t>
+          <t>17686</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33082</t>
+          <t>34138</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -8369,72 +8369,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>87112</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>78315</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>95663</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>71,57%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>64,34%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>78,59%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>78476</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>71288</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>84744</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>78,23%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>71,06%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>84,48%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>95904</t>
+          <t>73027</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>84853</t>
+          <t>65055</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>104410</t>
+          <t>79079</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>174381</t>
+          <t>160139</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>162218</t>
+          <t>147172</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>185488</t>
+          <t>170551</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>78,51%</t>
         </is>
       </c>
     </row>
@@ -8482,72 +8482,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>22053</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>15289</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>31228</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>18,12%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>12,56%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>25,66%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>10112</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>5958</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>16520</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>10,08%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,94%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>16,47%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22758</t>
+          <t>10191</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15061</t>
+          <t>6054</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33374</t>
+          <t>16180</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>32871</t>
+          <t>32244</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24229</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>43879</t>
+          <t>43899</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -8595,57 +8595,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
